--- a/pipelines/Demo_data/Output_data/out_Принтер_МФУ_сканер.xlsx
+++ b/pipelines/Demo_data/Output_data/out_Принтер_МФУ_сканер.xlsx
@@ -486,10 +486,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -530,10 +528,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -574,10 +570,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -618,10 +612,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -662,10 +654,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -706,10 +696,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -750,10 +738,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -794,10 +780,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -838,10 +822,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -882,10 +864,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,10 +906,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -970,10 +948,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1014,10 +990,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1058,10 +1032,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1102,10 +1074,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1146,10 +1116,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1190,10 +1158,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1234,10 +1200,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1278,10 +1242,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F20" t="n">
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1322,10 +1284,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1366,10 +1326,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1410,10 +1368,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F23" t="n">
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1454,10 +1410,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F24" t="n">
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1498,10 +1452,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F25" t="n">
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1542,10 +1494,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F26" t="n">
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1586,10 +1536,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F27" t="n">
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1630,10 +1578,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F28" t="n">
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1674,10 +1620,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F29" t="n">
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1718,10 +1662,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F30" t="n">
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1762,10 +1704,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F31" t="n">
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1806,10 +1746,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>983.79</t>
-        </is>
+      <c r="F32" t="n">
+        <v>983.79</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1850,10 +1788,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F33" t="n">
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1894,10 +1830,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F34" t="n">
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1938,10 +1872,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F35" t="n">
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1982,10 +1914,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F36" t="n">
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2026,10 +1956,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F37" t="n">
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2070,10 +1998,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F38" t="n">
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2114,10 +2040,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F39" t="n">
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2158,10 +2082,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F40" t="n">
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2202,10 +2124,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F41" t="n">
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2246,10 +2166,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F42" t="n">
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2290,10 +2208,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F43" t="n">
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2334,10 +2250,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F44" t="n">
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2378,10 +2292,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F45" t="n">
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2422,10 +2334,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F46" t="n">
+        <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2466,10 +2376,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F47" t="n">
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2510,10 +2418,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F48" t="n">
+        <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2554,10 +2460,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F49" t="n">
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2598,10 +2502,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F50" t="n">
+        <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2642,10 +2544,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F51" t="n">
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2686,10 +2586,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F52" t="n">
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2730,10 +2628,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F53" t="n">
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2774,10 +2670,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F54" t="n">
+        <v>0</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2818,10 +2712,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F55" t="n">
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2862,10 +2754,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F56" t="n">
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2906,10 +2796,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F57" t="n">
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2950,10 +2838,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F58" t="n">
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2994,10 +2880,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F59" t="n">
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3038,10 +2922,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F60" t="n">
+        <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3082,10 +2964,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F61" t="n">
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3126,10 +3006,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F62" t="n">
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3170,10 +3048,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F63" t="n">
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3214,10 +3090,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F64" t="n">
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3258,10 +3132,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F65" t="n">
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3302,10 +3174,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>79743.49</t>
-        </is>
+      <c r="F66" t="n">
+        <v>79743.49000000001</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3346,10 +3216,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>67990.29</t>
-        </is>
+      <c r="F67" t="n">
+        <v>67990.28999999999</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3390,10 +3258,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>80062.61</t>
-        </is>
+      <c r="F68" t="n">
+        <v>80062.61</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3434,10 +3300,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>68492.93</t>
-        </is>
+      <c r="F69" t="n">
+        <v>68492.92999999999</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3478,10 +3342,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>70908.17</t>
-        </is>
+      <c r="F70" t="n">
+        <v>70908.17</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3522,10 +3384,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>72364.16</t>
-        </is>
+      <c r="F71" t="n">
+        <v>72364.16</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3566,10 +3426,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>69813.55</t>
-        </is>
+      <c r="F72" t="n">
+        <v>69813.55</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3610,10 +3468,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>69904.88</t>
-        </is>
+      <c r="F73" t="n">
+        <v>69904.88</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3654,10 +3510,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>68624.74</t>
-        </is>
+      <c r="F74" t="n">
+        <v>68624.74000000001</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3698,10 +3552,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>79340.71</t>
-        </is>
+      <c r="F75" t="n">
+        <v>79340.71000000001</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3742,10 +3594,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F76" t="n">
+        <v>0</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3786,10 +3636,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F77" t="n">
+        <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3830,10 +3678,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F78" t="n">
+        <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3874,10 +3720,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F79" t="n">
+        <v>0</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3914,7 +3758,9 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>2017-10-16 00:00:00</t>
@@ -3946,7 +3792,9 @@
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>2017-10-16 00:00:00</t>
@@ -3982,10 +3830,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F82" t="n">
+        <v>0</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4026,10 +3872,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F83" t="n">
+        <v>0</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4070,10 +3914,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F84" t="n">
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4114,10 +3956,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F85" t="n">
+        <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4158,10 +3998,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F86" t="n">
+        <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4202,10 +4040,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F87" t="n">
+        <v>0</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4246,10 +4082,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F88" t="n">
+        <v>0</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4290,10 +4124,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F89" t="n">
+        <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4334,10 +4166,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F90" t="n">
+        <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4378,10 +4208,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F91" t="n">
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4422,10 +4250,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F92" t="n">
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4466,10 +4292,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F93" t="n">
+        <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4510,10 +4334,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F94" t="n">
+        <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4554,10 +4376,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F95" t="n">
+        <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4598,10 +4418,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F96" t="n">
+        <v>0</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4642,10 +4460,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F97" t="n">
+        <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4686,10 +4502,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F98" t="n">
+        <v>0</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4730,10 +4544,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F99" t="n">
+        <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4774,10 +4586,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F100" t="n">
+        <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4818,10 +4628,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F101" t="n">
+        <v>0</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4862,10 +4670,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F102" t="n">
+        <v>0</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4906,10 +4712,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F103" t="n">
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4950,10 +4754,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F104" t="n">
+        <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4994,10 +4796,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F105" t="n">
+        <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5038,10 +4838,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F106" t="n">
+        <v>0</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5082,10 +4880,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F107" t="n">
+        <v>0</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5126,10 +4922,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F108" t="n">
+        <v>0</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5170,10 +4964,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F109" t="n">
+        <v>0</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5214,10 +5006,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F110" t="n">
+        <v>0</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5258,10 +5048,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F111" t="n">
+        <v>0</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5302,10 +5090,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F112" t="n">
+        <v>0</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5346,10 +5132,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F113" t="n">
+        <v>0</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5390,10 +5174,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>70413.59</t>
-        </is>
+      <c r="F114" t="n">
+        <v>70413.59</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5434,10 +5216,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>81927.94</t>
-        </is>
+      <c r="F115" t="n">
+        <v>81927.94</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5478,10 +5258,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F116" t="n">
+        <v>0</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5522,10 +5300,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>76645.7</t>
-        </is>
+      <c r="F117" t="n">
+        <v>76645.7</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5566,10 +5342,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F118" t="n">
+        <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5610,10 +5384,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1023.75</t>
-        </is>
+      <c r="F119" t="n">
+        <v>1023.75</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5654,10 +5426,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>1023.75</t>
-        </is>
+      <c r="F120" t="n">
+        <v>1023.75</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5698,10 +5468,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F121" t="n">
+        <v>0</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5742,10 +5510,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F122" t="n">
+        <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5786,10 +5552,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F123" t="n">
+        <v>0</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5830,10 +5594,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>7509.3</t>
-        </is>
+      <c r="F124" t="n">
+        <v>7509.3</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -5874,10 +5636,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F125" t="n">
+        <v>0</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -5918,10 +5678,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>106796.99</t>
-        </is>
+      <c r="F126" t="n">
+        <v>106796.99</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -5962,10 +5720,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>91974.4</t>
-        </is>
+      <c r="F127" t="n">
+        <v>91974.39999999999</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -6006,10 +5762,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>91715.8</t>
-        </is>
+      <c r="F128" t="n">
+        <v>91715.8</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6050,10 +5804,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>93159.77</t>
-        </is>
+      <c r="F129" t="n">
+        <v>93159.77</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6094,10 +5846,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F130" t="n">
+        <v>0</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6138,10 +5888,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F131" t="n">
+        <v>0</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -6182,10 +5930,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F132" t="n">
+        <v>0</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -6226,10 +5972,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F133" t="n">
+        <v>0</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -6270,10 +6014,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F134" t="n">
+        <v>0</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -6314,10 +6056,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F135" t="n">
+        <v>0</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -6358,10 +6098,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F136" t="n">
+        <v>0</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -6402,10 +6140,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F137" t="n">
+        <v>0</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -6446,10 +6182,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F138" t="n">
+        <v>0</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -6490,10 +6224,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F139" t="n">
+        <v>0</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -6534,10 +6266,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F140" t="n">
+        <v>0</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -6578,10 +6308,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F141" t="n">
+        <v>0</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -6622,10 +6350,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F142" t="n">
+        <v>0</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -6666,10 +6392,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F143" t="n">
+        <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -6710,10 +6434,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F144" t="n">
+        <v>0</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -6754,10 +6476,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F145" t="n">
+        <v>0</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -6798,10 +6518,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F146" t="n">
+        <v>0</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -6842,10 +6560,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F147" t="n">
+        <v>0</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -6886,10 +6602,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F148" t="n">
+        <v>0</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -6930,10 +6644,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F149" t="n">
+        <v>0</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -6974,10 +6686,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F150" t="n">
+        <v>0</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -7018,10 +6728,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F151" t="n">
+        <v>0</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -7062,10 +6770,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F152" t="n">
+        <v>0</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -7106,10 +6812,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F153" t="n">
+        <v>0</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -7150,10 +6854,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F154" t="n">
+        <v>0</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -7194,10 +6896,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F155" t="n">
+        <v>0</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -7238,10 +6938,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F156" t="n">
+        <v>0</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -7282,10 +6980,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F157" t="n">
+        <v>0</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -7326,10 +7022,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F158" t="n">
+        <v>0</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -7370,10 +7064,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F159" t="n">
+        <v>0</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -7414,10 +7106,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F160" t="n">
+        <v>0</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -7458,10 +7148,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F161" t="n">
+        <v>0</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -7502,10 +7190,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F162" t="n">
+        <v>0</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -7546,10 +7232,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F163" t="n">
+        <v>0</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -7590,10 +7274,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F164" t="n">
+        <v>0</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -7634,10 +7316,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F165" t="n">
+        <v>0</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -7678,10 +7358,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F166" t="n">
+        <v>0</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -7722,10 +7400,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F167" t="n">
+        <v>0</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -7766,10 +7442,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F168" t="n">
+        <v>0</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -7810,10 +7484,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F169" t="n">
+        <v>0</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -7854,10 +7526,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F170" t="n">
+        <v>0</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -7898,10 +7568,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F171" t="n">
+        <v>0</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -7942,10 +7610,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F172" t="n">
+        <v>0</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -7994,10 +7660,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>94215.78</t>
-        </is>
+      <c r="F173" t="n">
+        <v>94215.78</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -8046,10 +7710,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>91393.87</t>
-        </is>
+      <c r="F174" t="n">
+        <v>91393.87</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -8098,10 +7760,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>98664.01</t>
-        </is>
+      <c r="F175" t="n">
+        <v>98664.00999999999</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -8150,10 +7810,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>112781.52</t>
-        </is>
+      <c r="F176" t="n">
+        <v>112781.52</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -8202,10 +7860,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>109104.32</t>
-        </is>
+      <c r="F177" t="n">
+        <v>109104.32</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>

--- a/pipelines/Demo_data/Output_data/out_Принтер_МФУ_сканер.xlsx
+++ b/pipelines/Demo_data/Output_data/out_Принтер_МФУ_сканер.xlsx
@@ -486,8 +486,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -528,8 +530,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -570,8 +574,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -612,8 +618,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -654,8 +662,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -696,8 +706,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -738,8 +750,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -780,8 +794,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -822,8 +838,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -864,8 +882,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -906,8 +926,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -948,8 +970,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -990,8 +1014,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1032,8 +1058,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1074,8 +1102,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1116,8 +1146,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1158,8 +1190,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1200,8 +1234,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1242,8 +1278,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1284,8 +1322,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1326,8 +1366,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1368,8 +1410,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1410,8 +1454,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1452,8 +1498,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1494,8 +1542,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1536,8 +1586,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1578,8 +1630,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1620,8 +1674,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1662,8 +1718,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1704,8 +1762,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1746,8 +1806,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>983.79</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>983.79</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1788,8 +1850,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1830,8 +1894,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1872,8 +1938,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1914,8 +1982,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1956,8 +2026,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1998,8 +2070,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2040,8 +2114,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2082,8 +2158,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2124,8 +2202,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2166,8 +2246,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2208,8 +2290,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2250,8 +2334,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2292,8 +2378,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2334,8 +2422,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2376,8 +2466,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>0</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2418,8 +2510,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2460,8 +2554,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2502,8 +2598,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>0</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2544,8 +2642,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2586,8 +2686,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>0</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2628,8 +2730,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2670,8 +2774,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2712,8 +2818,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2754,8 +2862,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>0</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2796,8 +2906,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>0</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2838,8 +2950,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>0</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2880,8 +2994,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2922,8 +3038,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2964,8 +3082,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>0</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3006,8 +3126,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>0</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3048,8 +3170,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3090,8 +3214,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>0</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3132,8 +3258,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>0</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3174,8 +3302,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>79743.49000000001</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>79743.49</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3216,8 +3346,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>67990.28999999999</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>67990.29</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3258,8 +3390,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>80062.61</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>80062.61</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3300,8 +3434,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>68492.92999999999</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>68492.93</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3342,8 +3478,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>70908.17</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>70908.17</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3384,8 +3522,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>72364.16</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>72364.16</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3426,8 +3566,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>69813.55</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69813.55</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3468,8 +3610,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>69904.88</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>69904.88</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3510,8 +3654,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>68624.74000000001</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>68624.74</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3552,8 +3698,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>79340.71000000001</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>79340.71</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3594,8 +3742,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3636,8 +3786,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3678,8 +3830,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>0</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3720,8 +3874,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>0</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3758,9 +3914,7 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>2017-10-16 00:00:00</t>
@@ -3792,9 +3946,7 @@
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>2017-10-16 00:00:00</t>
@@ -3830,8 +3982,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>0</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3872,8 +4026,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>0</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3914,8 +4070,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>0</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3956,8 +4114,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>0</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3998,8 +4158,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F86" t="n">
-        <v>0</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4040,8 +4202,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>0</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4082,8 +4246,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F88" t="n">
-        <v>0</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4124,8 +4290,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F89" t="n">
-        <v>0</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4166,8 +4334,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>0</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4208,8 +4378,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4250,8 +4422,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4292,8 +4466,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4334,8 +4510,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>0</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4376,8 +4554,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4418,8 +4598,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4460,8 +4642,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>0</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4502,8 +4686,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F98" t="n">
-        <v>0</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4544,8 +4730,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F99" t="n">
-        <v>0</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4586,8 +4774,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F100" t="n">
-        <v>0</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4628,8 +4818,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F101" t="n">
-        <v>0</v>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4670,8 +4862,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F102" t="n">
-        <v>0</v>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4712,8 +4906,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F103" t="n">
-        <v>0</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4754,8 +4950,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F104" t="n">
-        <v>0</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4796,8 +4994,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F105" t="n">
-        <v>0</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4838,8 +5038,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>0</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4880,8 +5082,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F107" t="n">
-        <v>0</v>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4922,8 +5126,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F108" t="n">
-        <v>0</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4964,8 +5170,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F109" t="n">
-        <v>0</v>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5006,8 +5214,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F110" t="n">
-        <v>0</v>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5048,8 +5258,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F111" t="n">
-        <v>0</v>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5090,8 +5302,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F112" t="n">
-        <v>0</v>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5132,8 +5346,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F113" t="n">
-        <v>0</v>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5174,8 +5390,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F114" t="n">
-        <v>70413.59</v>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>70413.59</t>
+        </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5216,8 +5434,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F115" t="n">
-        <v>81927.94</v>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>81927.94</t>
+        </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5258,8 +5478,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F116" t="n">
-        <v>0</v>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5300,8 +5522,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F117" t="n">
-        <v>76645.7</v>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>76645.7</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5342,8 +5566,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F118" t="n">
-        <v>0</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5384,8 +5610,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F119" t="n">
-        <v>1023.75</v>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1023.75</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5426,8 +5654,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F120" t="n">
-        <v>1023.75</v>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1023.75</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5468,8 +5698,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F121" t="n">
-        <v>0</v>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5510,8 +5742,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F122" t="n">
-        <v>0</v>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5552,8 +5786,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F123" t="n">
-        <v>0</v>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5594,8 +5830,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F124" t="n">
-        <v>7509.3</v>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>7509.3</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -5636,8 +5874,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F125" t="n">
-        <v>0</v>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -5678,8 +5918,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F126" t="n">
-        <v>106796.99</v>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>106796.99</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -5720,8 +5962,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F127" t="n">
-        <v>91974.39999999999</v>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>91974.4</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -5762,8 +6006,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F128" t="n">
-        <v>91715.8</v>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>91715.8</t>
+        </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5804,8 +6050,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F129" t="n">
-        <v>93159.77</v>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>93159.77</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -5846,8 +6094,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F130" t="n">
-        <v>0</v>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5888,8 +6138,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F131" t="n">
-        <v>0</v>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -5930,8 +6182,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F132" t="n">
-        <v>0</v>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -5972,8 +6226,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F133" t="n">
-        <v>0</v>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -6014,8 +6270,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F134" t="n">
-        <v>0</v>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -6056,8 +6314,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F135" t="n">
-        <v>0</v>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -6098,8 +6358,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F136" t="n">
-        <v>0</v>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -6140,8 +6402,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F137" t="n">
-        <v>0</v>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -6182,8 +6446,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F138" t="n">
-        <v>0</v>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -6224,8 +6490,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F139" t="n">
-        <v>0</v>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -6266,8 +6534,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F140" t="n">
-        <v>0</v>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -6308,8 +6578,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F141" t="n">
-        <v>0</v>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -6350,8 +6622,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F142" t="n">
-        <v>0</v>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -6392,8 +6666,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F143" t="n">
-        <v>0</v>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -6434,8 +6710,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F144" t="n">
-        <v>0</v>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -6476,8 +6754,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F145" t="n">
-        <v>0</v>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -6518,8 +6798,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F146" t="n">
-        <v>0</v>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -6560,8 +6842,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F147" t="n">
-        <v>0</v>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -6602,8 +6886,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F148" t="n">
-        <v>0</v>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -6644,8 +6930,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F149" t="n">
-        <v>0</v>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -6686,8 +6974,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F150" t="n">
-        <v>0</v>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -6728,8 +7018,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F151" t="n">
-        <v>0</v>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -6770,8 +7062,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F152" t="n">
-        <v>0</v>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -6812,8 +7106,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F153" t="n">
-        <v>0</v>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -6854,8 +7150,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F154" t="n">
-        <v>0</v>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -6896,8 +7194,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F155" t="n">
-        <v>0</v>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -6938,8 +7238,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F156" t="n">
-        <v>0</v>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -6980,8 +7282,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F157" t="n">
-        <v>0</v>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -7022,8 +7326,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F158" t="n">
-        <v>0</v>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -7064,8 +7370,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F159" t="n">
-        <v>0</v>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -7106,8 +7414,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F160" t="n">
-        <v>0</v>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -7148,8 +7458,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F161" t="n">
-        <v>0</v>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -7190,8 +7502,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F162" t="n">
-        <v>0</v>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -7232,8 +7546,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F163" t="n">
-        <v>0</v>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -7274,8 +7590,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F164" t="n">
-        <v>0</v>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -7316,8 +7634,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F165" t="n">
-        <v>0</v>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -7358,8 +7678,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F166" t="n">
-        <v>0</v>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -7400,8 +7722,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F167" t="n">
-        <v>0</v>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -7442,8 +7766,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F168" t="n">
-        <v>0</v>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -7484,8 +7810,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F169" t="n">
-        <v>0</v>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -7526,8 +7854,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F170" t="n">
-        <v>0</v>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -7568,8 +7898,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F171" t="n">
-        <v>0</v>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -7610,8 +7942,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F172" t="n">
-        <v>0</v>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -7660,8 +7994,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F173" t="n">
-        <v>94215.78</v>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>94215.78</t>
+        </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -7710,8 +8046,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F174" t="n">
-        <v>91393.87</v>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>91393.87</t>
+        </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -7760,8 +8098,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F175" t="n">
-        <v>98664.00999999999</v>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>98664.01</t>
+        </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -7810,8 +8150,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F176" t="n">
-        <v>112781.52</v>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>112781.52</t>
+        </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -7860,8 +8202,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F177" t="n">
-        <v>109104.32</v>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>109104.32</t>
+        </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
